--- a/public/templates/assessment.xlsx
+++ b/public/templates/assessment.xlsx
@@ -4,9 +4,13 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="③ 量表-清单" sheetId="1" r:id="rId1"/>
-    <sheet name="④ 量表-题目" sheetId="2" r:id="rId2"/>
-    <sheet name="④b 量表-选项组" sheetId="3" r:id="rId3"/>
-    <sheet name="④c 量表-维度定义" sheetId="4" r:id="rId4"/>
+    <sheet name="③a 量表编排指南" sheetId="2" r:id="rId2"/>
+    <sheet name="③b 角色说明" sheetId="3" r:id="rId3"/>
+    <sheet name="③c 路径示意" sheetId="4" r:id="rId4"/>
+    <sheet name="③d 编排自检" sheetId="5" r:id="rId5"/>
+    <sheet name="④ 量表-题目" sheetId="6" r:id="rId6"/>
+    <sheet name="④b 量表-选项组" sheetId="7" r:id="rId7"/>
+    <sheet name="④c 量表-维度定义" sheetId="8" r:id="rId8"/>
   </sheets>
 </workbook>
 </file>
@@ -400,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AH1"/>
+  <dimension ref="A1:AL1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -461,59 +465,716 @@
         <v>互斥量表编码</v>
       </c>
       <c r="T1" t="str">
+        <v>触发条件</v>
+      </c>
+      <c r="U1" t="str">
+        <v>触发条件说明</v>
+      </c>
+      <c r="V1" t="str">
         <v>结果可见性*</v>
       </c>
-      <c r="U1" t="str">
+      <c r="W1" t="str">
         <v>责任角色</v>
       </c>
-      <c r="V1" t="str">
+      <c r="X1" t="str">
         <v>数据敏感级*</v>
       </c>
-      <c r="W1" t="str">
+      <c r="Y1" t="str">
         <v>来源属性*</v>
       </c>
-      <c r="X1" t="str">
+      <c r="Z1" t="str">
         <v>外部授权说明</v>
       </c>
-      <c r="Y1" t="str">
+      <c r="AA1" t="str">
         <v>手册出处*</v>
       </c>
-      <c r="Z1" t="str">
+      <c r="AB1" t="str">
         <v>版本*</v>
       </c>
-      <c r="AA1" t="str">
+      <c r="AC1" t="str">
         <v>量表说明</v>
       </c>
-      <c r="AB1" t="str">
+      <c r="AD1" t="str">
         <v>常模参照</v>
       </c>
-      <c r="AC1" t="str">
+      <c r="AE1" t="str">
         <v>信度说明</v>
       </c>
-      <c r="AD1" t="str">
+      <c r="AF1" t="str">
         <v>效度说明</v>
       </c>
-      <c r="AE1" t="str">
+      <c r="AG1" t="str">
         <v>隐私声明</v>
       </c>
-      <c r="AF1" t="str">
+      <c r="AH1" t="str">
         <v>适用前提</v>
       </c>
-      <c r="AG1" t="str">
+      <c r="AI1" t="str">
         <v>不适合情况</v>
       </c>
-      <c r="AH1" t="str">
+      <c r="AJ1" t="str">
         <v>后续建议动作</v>
+      </c>
+      <c r="AK1" t="str">
+        <v>量表角色*</v>
+      </c>
+      <c r="AL1" t="str">
+        <v>做完导向什么*</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AH1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AL1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A36"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>量表编排 —— 一个模块有多张量表时，先填这一步</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>【为什么需要这一步】</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>20~25 张量表如果不先定角色和关系，导进系统就是一堆互不相干的问卷：</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v xml:space="preserve">  · 教师打开模块，看到四五张量表，不知道该做哪张</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v xml:space="preserve">  · AI 推荐没有确定性依据，只能看题目名称猜</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v xml:space="preserve">  · 深度量表没有触发条件，要么没人做，要么所有人都做一遍</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>【怎么做】</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>第1步  给每张量表定角色 —— 见 ③b 角色说明</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>第2步  回答下面三个问题，答不上来的量表说明它不该独立存在</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>第3步  把结论直接填进 ③ 量表-清单 的这六列：</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v xml:space="preserve">       是否必做 / 前置量表编码 / 互斥量表编码 / 触发条件 / 量表角色 / 做完导向什么</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v xml:space="preserve">       其中「量表角色」「做完导向什么」不进系统，只是留痕，方便复盘和交接。</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>【每张量表必须能回答的三个问题】</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>问题一：它测的东西，别的量表测不了吗？</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v xml:space="preserve">        答不上来 → 合并。两张量表的维度大量重叠时，教师做完第一张就没有做第二张的动力。</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>问题二：什么情况下该做它？</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v xml:space="preserve">        这个答案就是「触发条件」那一列。答不上来 → 它没有明确使用时机，等于永远没人做。</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>问题三：做完之后能得出什么行动？</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v xml:space="preserve">        这个答案就是「做完导向什么」那一列。答不上来 → 它只是问卷不是量表。</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v xml:space="preserve">        典型症状：能算出归因，但等级恒定、推不出工具。</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>【前置量表 vs 触发条件，两者不是一回事】</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>前置量表：硬门禁。没做完前置，这张量表在教师端置灰、点不动。</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>触发条件：软推荐。没达到阈值只标「当前不需要做」，教师仍可手动选择。</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v xml:space="preserve">          业务的阈值是经验判断，不该把教师锁死在系统的判断里。</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>两列都留空 = 这张量表随时可做。留空即放行，不会因为加了门禁反而把量表锁死。</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>【触发条件怎么写】引用前面量表的结果，语法与归因库一致</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v xml:space="preserve">  量表[SG_FIVE_Q].总分 &gt;= 17</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v xml:space="preserve">  量表[SG_FIVE_Q].维度[SG_EMOTION] &gt;= 4 或 量表[SG_FIVE_Q].等级 == 'orange'</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v xml:space="preserve">  量表[HS_QUICK].已完成 == 1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>完整写法见 ⑤a 条件写法速查 的最后一段。</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>写错会被导入校验直接拦下（语法错、引用了不存在的量表编码都会报错），不会带进系统静默失效。</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:A36"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G7"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>量表角色</v>
+      </c>
+      <c r="B1" t="str">
+        <v>特征</v>
+      </c>
+      <c r="C1" t="str">
+        <v>每模块建议数量</v>
+      </c>
+      <c r="D1" t="str">
+        <v>是否必做</v>
+      </c>
+      <c r="E1" t="str">
+        <v>前置量表</v>
+      </c>
+      <c r="F1" t="str">
+        <v>触发条件</v>
+      </c>
+      <c r="G1" t="str">
+        <v>典型例子</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>入口筛查</v>
+      </c>
+      <c r="B2" t="str">
+        <v>快（3-6 题）、覆盖广，决定要不要往下走</v>
+      </c>
+      <c r="C2" t="str">
+        <v>1 张</v>
+      </c>
+      <c r="D2" t="str">
+        <v>是</v>
+      </c>
+      <c r="E2" t="str">
+        <v>不填</v>
+      </c>
+      <c r="F2" t="str">
+        <v>不填</v>
+      </c>
+      <c r="G2" t="str">
+        <v>班主任状态五问、家校双维速查</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>深度诊断</v>
+      </c>
+      <c r="B3" t="str">
+        <v>慢、精准，只在筛查报警时做</v>
+      </c>
+      <c r="C3" t="str">
+        <v>1-2 张</v>
+      </c>
+      <c r="D3" t="str">
+        <v>否</v>
+      </c>
+      <c r="E3" t="str">
+        <v>填筛查量表</v>
+      </c>
+      <c r="F3" t="str">
+        <v>填筛查的阈值</v>
+      </c>
+      <c r="G3" t="str">
+        <v>心理资本深度评估、六维度诊断</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>专项/情境</v>
+      </c>
+      <c r="B4" t="str">
+        <v>针对特定场景，可能与别的量表互斥</v>
+      </c>
+      <c r="C4" t="str">
+        <v>1-2 张</v>
+      </c>
+      <c r="D4" t="str">
+        <v>否</v>
+      </c>
+      <c r="E4" t="str">
+        <v>视情况</v>
+      </c>
+      <c r="F4" t="str">
+        <v>填情境判断条件</v>
+      </c>
+      <c r="G4" t="str">
+        <v>家长分型、能量场问卷</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>红线检查</v>
+      </c>
+      <c r="B5" t="str">
+        <v>是非勾选清单，安全兜底，不该由教师主动选</v>
+      </c>
+      <c r="C5" t="str">
+        <v>0-1 张</v>
+      </c>
+      <c r="D5" t="str">
+        <v>否</v>
+      </c>
+      <c r="E5" t="str">
+        <v>填筛查量表</v>
+      </c>
+      <c r="F5" t="str">
+        <v>填高危阈值</v>
+      </c>
+      <c r="G5" t="str">
+        <v>触发条件筛查清单</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v/>
+      </c>
+      <c r="B6" t="str">
+        <v/>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>合计</v>
+      </c>
+      <c r="B7" t="str">
+        <v>1 入口 + 1-2 深度 + 1-2 专项 + 0-1 红线 = 每模块 3-5 张</v>
+      </c>
+      <c r="C7" t="str">
+        <v>5 模块共 15-25 张</v>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G7"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E24"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>以家校沟通模块为例，梳理后的路径</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>HS_QUICK（入口筛查，必做，9 题）</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v xml:space="preserve">   ├─ 总分 &lt; 18   → 结束，A 级常规沟通，不需要做其他量表</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v xml:space="preserve">   ├─ 总分 &gt;= 18  → 触发 HS_DIM6（深度诊断：定位六个维度里哪个塌了）</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v xml:space="preserve">   └─ 题[att3] &gt;= 4 → 触发 HS_TRIGGER（红线检查表：确认是否走 E 级保护通道）</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>HS_PARENT_TYPE（专项，6 题）</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v xml:space="preserve">   └─ 触发条件：量表[HS_QUICK].维度[HS_ATTITUDE] &gt;= 3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v xml:space="preserve">      沟通态度有问题时才需要判断家长类型，否则不用做</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>对应到 ③ 量表-清单 就是这样填：</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>量表编码</v>
+      </c>
+      <c r="B14" t="str">
+        <v>是否必做</v>
+      </c>
+      <c r="C14" t="str">
+        <v>前置量表编码</v>
+      </c>
+      <c r="D14" t="str">
+        <v>触发条件</v>
+      </c>
+      <c r="E14" t="str">
+        <v>量表角色</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>HS_QUICK</v>
+      </c>
+      <c r="B15" t="str">
+        <v>是</v>
+      </c>
+      <c r="C15" t="str">
+        <v/>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+      <c r="E15" t="str">
+        <v>入口筛查</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>HS_DIM6</v>
+      </c>
+      <c r="B16" t="str">
+        <v>否</v>
+      </c>
+      <c r="C16" t="str">
+        <v>HS_QUICK</v>
+      </c>
+      <c r="D16" t="str">
+        <v>量表[HS_QUICK].总分 &gt;= 18</v>
+      </c>
+      <c r="E16" t="str">
+        <v>深度诊断</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>HS_TRIGGER</v>
+      </c>
+      <c r="B17" t="str">
+        <v>否</v>
+      </c>
+      <c r="C17" t="str">
+        <v>HS_QUICK</v>
+      </c>
+      <c r="D17" t="str">
+        <v>量表[HS_QUICK].题[att3] &gt;= 4</v>
+      </c>
+      <c r="E17" t="str">
+        <v>红线检查</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>HS_PARENT_TYPE</v>
+      </c>
+      <c r="B18" t="str">
+        <v>否</v>
+      </c>
+      <c r="C18" t="str">
+        <v>HS_QUICK</v>
+      </c>
+      <c r="D18" t="str">
+        <v>量表[HS_QUICK].维度[HS_ATTITUDE] &gt;= 3</v>
+      </c>
+      <c r="E18" t="str">
+        <v>专项/情境</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>填完之后教师端会自动呈现：</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v xml:space="preserve">  · 只做过速评且分数低 → 只有速评显示「已完成」，其余三张标「当前不需要」</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v xml:space="preserve">  · 速评总分 18 分以上 → 六维度诊断自动标「建议做」并排到最前</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v xml:space="preserve">  · 速评 att3 达到 4 分 → 红线检查表标「建议做」</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v xml:space="preserve">  · 没做速评 → 其余三张全部置灰，提示「请先完成 家校沟通双维与容器速查」</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E24"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>自检项</v>
+      </c>
+      <c r="B1" t="str">
+        <v>不通过的后果</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>每个模块有且只有一张「入口筛查」，且是唯一标「是否必做=是」的</v>
+      </c>
+      <c r="B2" t="str">
+        <v>教师进模块不知道从哪开始</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>每张深度/专项/红线量表都填了「前置量表编码」</v>
+      </c>
+      <c r="B3" t="str">
+        <v>教师可能在没有基线的情况下直接做深度量表</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>每张非入口量表都填了「触发条件」</v>
+      </c>
+      <c r="B4" t="str">
+        <v>要么没人做，要么所有人都做一遍，深度量表失去意义</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>触发条件引用的量表编码真实存在、表达式语法正确</v>
+      </c>
+      <c r="B5" t="str">
+        <v>条件永远不满足，量表永远显示「当前不需要做」（导入时会报错）</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>⑤e 分级规则里，每张量表都有至少一条「依据量表编码 = 该量表」且带触发条件的规则</v>
+      </c>
+      <c r="B6" t="str">
+        <v>该量表等级恒定，与归因结论自相矛盾（导入时会报错）</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>⑩ 输出模板覆盖了每张量表可能产出的所有等级</v>
+      </c>
+      <c r="B7" t="str">
+        <v>该等级的方案文案空缺</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>两张量表的维度没有大量重叠</v>
+      </c>
+      <c r="B8" t="str">
+        <v>教师做完第一张就没有做第二张的动力</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>每张量表都能回答「做完之后能得出什么行动」</v>
+      </c>
+      <c r="B9" t="str">
+        <v>它只是问卷不是量表</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>红线检查类量表没有标成「必做」</v>
+      </c>
+      <c r="B10" t="str">
+        <v>教师会被要求主动做一张本该自动触发的清单</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B10"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:P1"/>
   <sheetData>
@@ -574,7 +1235,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D1"/>
   <sheetData>
@@ -599,7 +1260,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K1"/>
   <sheetData>
